--- a/Result/profitability/8289.xlsx
+++ b/Result/profitability/8289.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05624999999999999</v>
+        <v>0.13375</v>
       </c>
       <c r="N2" t="n">
-        <v>23.44875</v>
+        <v>23.95375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.51</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1525</v>
+        <v>0.17875</v>
       </c>
       <c r="N3" t="n">
-        <v>23.80625</v>
+        <v>23.8425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.67</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2175</v>
+        <v>0.25375</v>
       </c>
       <c r="N4" t="n">
-        <v>23.93625</v>
+        <v>24.14125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2175</v>
+        <v>0.32</v>
       </c>
       <c r="N5" t="n">
-        <v>23.0175</v>
+        <v>22.76875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2975</v>
+        <v>0.32375</v>
       </c>
       <c r="N6" t="n">
-        <v>21.95625</v>
+        <v>22.09625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>0.26125</v>
+        <v>0.27125</v>
       </c>
       <c r="N7" t="n">
-        <v>21.15875</v>
+        <v>21.3625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>0.23125</v>
+        <v>0.24125</v>
       </c>
       <c r="N8" t="n">
-        <v>20.90625</v>
+        <v>20.935</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8289</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>510</v>
+      </c>
+      <c r="D75" t="n">
+        <v>387</v>
+      </c>
+      <c r="E75" t="n">
+        <v>123</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>32</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>32</v>
+      </c>
+      <c r="K75" t="n">
+        <v>24</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.07124999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.07999999999999996</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2857142857142856</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.2300000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.009655751469353602</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.782608695652174</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.989999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07642089093701987</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
